--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,352 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122833723</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lill-Rörsvallen, Kall, Lill-Rörsvallen, Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>401780</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7045001</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Ahlgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Ahlgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122833808</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lill-Rörsvallen, Kall, Lill-Rörsvallen, Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>401774</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7045153</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Ahlgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Ahlgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122833781</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lill-Rörsvallen, Kall, Lill-Rörsvallen, Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>401840</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7045073</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Ahlgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Ahlgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833723</v>
+        <v>122833781</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401780</v>
+        <v>401840</v>
       </c>
       <c r="R4" t="n">
-        <v>7045001</v>
+        <v>7045073</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833808</v>
+        <v>122833723</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1052,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401774</v>
+        <v>401780</v>
       </c>
       <c r="R5" t="n">
-        <v>7045153</v>
+        <v>7045001</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,6 +1112,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833781</v>
+        <v>122833808</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1178,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401840</v>
+        <v>401774</v>
       </c>
       <c r="R6" t="n">
-        <v>7045073</v>
+        <v>7045153</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,11 +1229,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833781</v>
+        <v>122833808</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401840</v>
+        <v>401774</v>
       </c>
       <c r="R4" t="n">
-        <v>7045073</v>
+        <v>7045153</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,11 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833723</v>
+        <v>122833781</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1052,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401780</v>
+        <v>401840</v>
       </c>
       <c r="R5" t="n">
-        <v>7045001</v>
+        <v>7045073</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833808</v>
+        <v>122833723</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1169,7 +1164,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401774</v>
+        <v>401780</v>
       </c>
       <c r="R6" t="n">
-        <v>7045153</v>
+        <v>7045001</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,6 +1224,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833808</v>
+        <v>122833723</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401774</v>
+        <v>401780</v>
       </c>
       <c r="R4" t="n">
-        <v>7045153</v>
+        <v>7045001</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,6 +995,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1128,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833723</v>
+        <v>122833808</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1164,7 +1169,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1178,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401780</v>
+        <v>401774</v>
       </c>
       <c r="R6" t="n">
-        <v>7045001</v>
+        <v>7045153</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,11 +1229,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833781</v>
+        <v>122833808</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401840</v>
+        <v>401774</v>
       </c>
       <c r="R5" t="n">
-        <v>7045073</v>
+        <v>7045153</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,11 +1112,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1133,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833808</v>
+        <v>122833781</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401774</v>
+        <v>401840</v>
       </c>
       <c r="R6" t="n">
-        <v>7045153</v>
+        <v>7045073</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,6 +1224,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833723</v>
+        <v>122833808</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401780</v>
+        <v>401774</v>
       </c>
       <c r="R4" t="n">
-        <v>7045001</v>
+        <v>7045153</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,11 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833808</v>
+        <v>122833781</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401774</v>
+        <v>401840</v>
       </c>
       <c r="R5" t="n">
-        <v>7045153</v>
+        <v>7045073</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,6 +1107,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833781</v>
+        <v>122833723</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1164,7 +1164,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401840</v>
+        <v>401780</v>
       </c>
       <c r="R6" t="n">
-        <v>7045073</v>
+        <v>7045001</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833781</v>
+        <v>122833723</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1047,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401840</v>
+        <v>401780</v>
       </c>
       <c r="R5" t="n">
-        <v>7045073</v>
+        <v>7045001</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833723</v>
+        <v>122833781</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1164,7 +1164,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401780</v>
+        <v>401840</v>
       </c>
       <c r="R6" t="n">
-        <v>7045001</v>
+        <v>7045073</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833808</v>
+        <v>122833723</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401774</v>
+        <v>401780</v>
       </c>
       <c r="R4" t="n">
-        <v>7045153</v>
+        <v>7045001</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,6 +995,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833723</v>
+        <v>122833781</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1047,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401780</v>
+        <v>401840</v>
       </c>
       <c r="R5" t="n">
-        <v>7045001</v>
+        <v>7045073</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833781</v>
+        <v>122833808</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1178,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401840</v>
+        <v>401774</v>
       </c>
       <c r="R6" t="n">
-        <v>7045073</v>
+        <v>7045153</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,11 +1229,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833723</v>
+        <v>122833808</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401780</v>
+        <v>401774</v>
       </c>
       <c r="R4" t="n">
-        <v>7045001</v>
+        <v>7045153</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,11 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833781</v>
+        <v>122833723</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1052,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401840</v>
+        <v>401780</v>
       </c>
       <c r="R5" t="n">
-        <v>7045073</v>
+        <v>7045001</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1133,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833808</v>
+        <v>122833781</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401774</v>
+        <v>401840</v>
       </c>
       <c r="R6" t="n">
-        <v>7045153</v>
+        <v>7045073</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,6 +1224,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833808</v>
+        <v>122833723</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401774</v>
+        <v>401780</v>
       </c>
       <c r="R4" t="n">
-        <v>7045153</v>
+        <v>7045001</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,6 +995,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833723</v>
+        <v>122833808</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401780</v>
+        <v>401774</v>
       </c>
       <c r="R5" t="n">
-        <v>7045001</v>
+        <v>7045153</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,11 +1112,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         <v>122833781</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833723</v>
+        <v>122833808</v>
       </c>
       <c r="B4" t="n">
         <v>57481</v>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401780</v>
+        <v>401774</v>
       </c>
       <c r="R4" t="n">
-        <v>7045001</v>
+        <v>7045153</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,11 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833808</v>
+        <v>122833723</v>
       </c>
       <c r="B5" t="n">
         <v>57481</v>
@@ -1052,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401774</v>
+        <v>401780</v>
       </c>
       <c r="R5" t="n">
-        <v>7045153</v>
+        <v>7045001</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,6 +1107,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 61875-2024 artfynd.xlsx
+++ b/artfynd/A 61875-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>120538234</v>
       </c>
       <c r="B2" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -790,12 +785,7 @@
         <v>120538190</v>
       </c>
       <c r="B3" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122833808</v>
+        <v>122833723</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -949,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401774</v>
+        <v>401780</v>
       </c>
       <c r="R4" t="n">
-        <v>7045153</v>
+        <v>7045001</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,6 +980,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122833723</v>
+        <v>122833781</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1032,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1061,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401780</v>
+        <v>401840</v>
       </c>
       <c r="R5" t="n">
-        <v>7045001</v>
+        <v>7045073</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,15 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122833781</v>
+        <v>122833808</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401840</v>
+        <v>401774</v>
       </c>
       <c r="R6" t="n">
-        <v>7045073</v>
+        <v>7045153</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,11 +1204,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
